--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260807.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260807.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>78,007</t>
+          <t>76,207</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>11.42%</t>
+          <t>11.40%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>32,296</t>
+          <t>31,596</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.55%</t>
+          <t>10.43%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>90,125</t>
+          <t>88,025</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.10%</t>
+          <t>7.99%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>35,455</t>
+          <t>34,655</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.73%</t>
+          <t>7.76%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>194,656</t>
+          <t>190,256</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.38%</t>
+          <t>5.37%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>103,491</t>
+          <t>101,191</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.19%</t>
+          <t>4.21%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>48,895</t>
+          <t>47,795</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.66%</t>
+          <t>3.50%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>112,266</t>
+          <t>109,766</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.41%</t>
+          <t>3.39%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>19,279</t>
+          <t>18,879</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>3.24%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>58,759</t>
+          <t>57,459</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>3.15%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>116,783</t>
+          <t>114,183</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.57%</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>54,127</t>
+          <t>52,827</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>135,901</t>
+          <t>132,901</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>2.02%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>24,204</t>
+          <t>23,704</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>22,431</t>
+          <t>21,931</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>62,103</t>
+          <t>60,703</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.58%</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>36,680</t>
+          <t>35,880</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>49,636</t>
+          <t>48,536</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>76,801</t>
+          <t>75,101</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>49,960</t>
+          <t>48,760</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>46,927</t>
+          <t>45,827</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>32,410</t>
+          <t>31,710</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1095,12 +1095,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>51,110</t>
+          <t>49,910</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>94,763</t>
+          <t>92,663</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>30,345</t>
+          <t>29,645</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>22,158</t>
+          <t>21,658</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,83 +1173,83 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>MTZ US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>MasTec公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>27,469</t>
+          <t>11,037</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>MTZ US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>MasTec公司</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>11,337</t>
+          <t>26,869</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>9,004</t>
+          <t>4,821</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>4,921</t>
+          <t>8,804</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>20,609</t>
+          <t>20,209</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1293,78 +1293,78 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>74,874</t>
+          <t>73,174</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>EVRG US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Evergy公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>30,214</t>
+          <t>12,952</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>13,252</t>
+          <t>142,245</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>EVRG US</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>Evergy公司</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>145,545</t>
+          <t>29,514</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>10,646</t>
+          <t>10,346</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>30,591</t>
+          <t>29,891</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>43,383</t>
+          <t>25,181</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,22 +1459,22 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>25,681</t>
+          <t>42,383</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>16,127</t>
+          <t>15,727</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>13,424</t>
+          <t>13,124</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>6,827</t>
+          <t>6,627</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>94,202</t>
+          <t>92,102</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>5,878</t>
+          <t>5,778</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>3,651</t>
+          <t>3,551</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>23,419</t>
+          <t>22,919</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>2,839</t>
+          <t>2,739</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>8,021</t>
+          <t>7,821</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>18,353</t>
+          <t>17,953</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>38,161</t>
+          <t>37,261</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>118,353,203</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
